--- a/cet4/result/06_豪门契约_冰山总裁的替身娇妻/06_豪门契约_冰山总裁的替身娇妻_学习版.xlsx
+++ b/cet4/result/06_豪门契约_冰山总裁的替身娇妻/06_豪门契约_冰山总裁的替身娇妻_学习版.xlsx
@@ -397,815 +397,703 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D49"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>cloud</v>
       </c>
       <c r="B2" t="str">
-        <v>cloud</v>
+        <v>/klaʊd/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D2" t="str">
         <v>云</v>
       </c>
-      <c r="D2" t="str">
-        <v>cloud(云)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>airport</v>
       </c>
       <c r="B3" t="str">
-        <v>airport</v>
+        <v>/ˈerpɔːrt/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>机场</v>
       </c>
-      <c r="D3" t="str">
-        <v>airport(机场)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>departure</v>
       </c>
       <c r="B4" t="str">
-        <v>departure</v>
+        <v>/dɪˈpɑːrtʃər/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>离开</v>
       </c>
-      <c r="D4" t="str">
-        <v>departure(离开)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>two</v>
       </c>
       <c r="B5" t="str">
-        <v>two</v>
+        <v>/tuː/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./adj./num.</v>
+      </c>
+      <c r="D5" t="str">
         <v>二</v>
       </c>
-      <c r="D5" t="str">
-        <v>two(二)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>girl</v>
       </c>
       <c r="B6" t="str">
-        <v>girl</v>
+        <v>/ɡɜːrl/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>女孩</v>
       </c>
-      <c r="D6" t="str">
-        <v>girl(女孩)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>flash</v>
       </c>
       <c r="B7" t="str">
-        <v>flash</v>
+        <v>/flæʃ/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>闪光</v>
       </c>
-      <c r="D7" t="str">
-        <v>flash(闪光)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>electricity</v>
       </c>
       <c r="B8" t="str">
-        <v>electricity</v>
+        <v>/ɪˌlekˈtrɪsəti/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>电力</v>
       </c>
-      <c r="D8" t="str">
-        <v>electricity(电力)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>assign</v>
       </c>
       <c r="B9" t="str">
-        <v>assign</v>
+        <v>/əˈsaɪn/</v>
       </c>
       <c r="C9" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D9" t="str">
         <v>分配</v>
       </c>
-      <c r="D9" t="str">
-        <v>assign(分配)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>clear</v>
       </c>
       <c r="B10" t="str">
-        <v>clear</v>
+        <v>/klɪr/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D10" t="str">
         <v>清楚的</v>
       </c>
-      <c r="D10" t="str">
-        <v>clear(清楚的)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>anchor</v>
       </c>
       <c r="B11" t="str">
-        <v>anchor</v>
+        <v>/ˈæŋkər/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>抛锚</v>
       </c>
-      <c r="D11" t="str">
-        <v>anchor(抛锚)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>thrust</v>
       </c>
       <c r="B12" t="str">
-        <v>thrust</v>
+        <v>/θrʌst/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D12" t="str">
         <v>推挤</v>
       </c>
-      <c r="D12" t="str">
-        <v>thrust(推挤)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>empire</v>
       </c>
       <c r="B13" t="str">
-        <v>empire</v>
+        <v>/ˈempaɪər/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>帝国</v>
       </c>
-      <c r="D13" t="str">
-        <v>empire(帝国)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>hide</v>
       </c>
       <c r="B14" t="str">
-        <v>two</v>
+        <v>/haɪd/</v>
       </c>
       <c r="C14" t="str">
-        <v>二</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D14" t="str">
-        <v>two(二)📢</v>
+        <v>隐藏</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>oh</v>
       </c>
       <c r="B15" t="str">
-        <v>hide</v>
+        <v>/oʊ/</v>
       </c>
       <c r="C15" t="str">
-        <v>隐藏</v>
+        <v>int.</v>
       </c>
       <c r="D15" t="str">
-        <v>hide(隐藏)📢</v>
+        <v>哦</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>offer</v>
       </c>
       <c r="B16" t="str">
-        <v>oh</v>
+        <v>/ˈɔːfər/</v>
       </c>
       <c r="C16" t="str">
-        <v>哦</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D16" t="str">
-        <v>oh(哦)📢</v>
+        <v>提供</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>whatever</v>
       </c>
       <c r="B17" t="str">
-        <v>offer</v>
+        <v>/wətˈevər/</v>
       </c>
       <c r="C17" t="str">
-        <v>提供</v>
+        <v>n./adj./pron.</v>
       </c>
       <c r="D17" t="str">
-        <v>offer(提供)📢</v>
+        <v>无论怎样的</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>recorder</v>
       </c>
       <c r="B18" t="str">
-        <v>whatever</v>
+        <v>/rɪˈkɔːrdər/</v>
       </c>
       <c r="C18" t="str">
-        <v>无论怎样的</v>
+        <v>n.</v>
       </c>
       <c r="D18" t="str">
-        <v>whatever(无论怎样的)📢</v>
+        <v>录音机</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>tempt</v>
       </c>
       <c r="B19" t="str">
-        <v>recorder</v>
+        <v>/tempt/</v>
       </c>
       <c r="C19" t="str">
-        <v>录音机</v>
+        <v>vt.</v>
       </c>
       <c r="D19" t="str">
-        <v>recorder(录音机)📢</v>
+        <v>诱惑</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>yellow</v>
       </c>
       <c r="B20" t="str">
-        <v>tempt</v>
+        <v>/ˈjeloʊ/</v>
       </c>
       <c r="C20" t="str">
-        <v>诱惑</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D20" t="str">
-        <v>tempt(诱惑)📢</v>
+        <v>黄色的</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>tear</v>
       </c>
       <c r="B21" t="str">
-        <v>yellow</v>
+        <v>/ˈtɛː;ˈtɪə/</v>
       </c>
       <c r="C21" t="str">
-        <v>黄色的</v>
+        <v>n./v.</v>
       </c>
       <c r="D21" t="str">
-        <v>yellow(黄色的)📢</v>
+        <v>眼泪</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>creep</v>
       </c>
       <c r="B22" t="str">
-        <v>tear</v>
+        <v>/kriːp/</v>
       </c>
       <c r="C22" t="str">
-        <v>眼泪</v>
+        <v>n./vi.</v>
       </c>
       <c r="D22" t="str">
-        <v>tear(眼泪)📢</v>
+        <v>爬行</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>smoothly</v>
       </c>
       <c r="B23" t="str">
-        <v>creep</v>
+        <v>/ˈsmuːðli/</v>
       </c>
       <c r="C23" t="str">
-        <v>爬行</v>
+        <v>v./adv.</v>
       </c>
       <c r="D23" t="str">
-        <v>creep(爬行)📢</v>
+        <v>平稳地</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>strength</v>
       </c>
       <c r="B24" t="str">
-        <v>smoothly</v>
+        <v>/streŋkθ/</v>
       </c>
       <c r="C24" t="str">
-        <v>平稳地</v>
+        <v>n.</v>
       </c>
       <c r="D24" t="str">
-        <v>smoothly(平稳地)📢</v>
+        <v>力量</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>vain</v>
       </c>
       <c r="B25" t="str">
-        <v>strength</v>
+        <v>/veɪn/</v>
       </c>
       <c r="C25" t="str">
-        <v>力量</v>
+        <v>adj.</v>
       </c>
       <c r="D25" t="str">
-        <v>strength(力量)📢</v>
+        <v>徒劳的</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>ornament</v>
       </c>
       <c r="B26" t="str">
-        <v>vain</v>
+        <v>/ˈɔːrnəmənt/</v>
       </c>
       <c r="C26" t="str">
-        <v>徒劳的</v>
+        <v>n./vt.</v>
       </c>
       <c r="D26" t="str">
-        <v>vain(徒劳的)📢</v>
+        <v>装饰物</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>sympathize</v>
       </c>
       <c r="B27" t="str">
-        <v>ornament</v>
+        <v>/ˈsɪmpəθaɪz/</v>
       </c>
       <c r="C27" t="str">
-        <v>装饰物</v>
+        <v>vi.</v>
       </c>
       <c r="D27" t="str">
-        <v>ornament(装饰物)📢</v>
+        <v>同情</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>unable</v>
       </c>
       <c r="B28" t="str">
-        <v>sympathize</v>
+        <v>/ʌnˈeɪbl/</v>
       </c>
       <c r="C28" t="str">
-        <v>同情</v>
+        <v>adj.</v>
       </c>
       <c r="D28" t="str">
-        <v>sympathize(同情)📢</v>
+        <v>不能的</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>exposure</v>
       </c>
       <c r="B29" t="str">
-        <v>unable</v>
+        <v>/ɪkˈspoʊʒər/</v>
       </c>
       <c r="C29" t="str">
-        <v>不能的</v>
+        <v>n.</v>
       </c>
       <c r="D29" t="str">
-        <v>unable(不能的)📢</v>
+        <v>曝光</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>chemical</v>
       </c>
       <c r="B30" t="str">
-        <v>exposure</v>
+        <v>/ˈkemɪkl/</v>
       </c>
       <c r="C30" t="str">
-        <v>曝光</v>
+        <v>n./adj.</v>
       </c>
       <c r="D30" t="str">
-        <v>exposure(曝光)📢</v>
+        <v>化学</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>dissatisfy</v>
       </c>
       <c r="B31" t="str">
-        <v>chemical</v>
+        <v>/dɪs'sætɪs,fai/</v>
       </c>
       <c r="C31" t="str">
-        <v>化学</v>
+        <v>v.</v>
       </c>
       <c r="D31" t="str">
-        <v>chemical(化学)📢</v>
+        <v>使不满</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>slam</v>
       </c>
       <c r="B32" t="str">
-        <v>dissatisfy</v>
+        <v>/slæm/</v>
       </c>
       <c r="C32" t="str">
-        <v>使不满</v>
+        <v>n./v.</v>
       </c>
       <c r="D32" t="str">
-        <v>dissatisfy(使不满)📢</v>
+        <v>砰地关上</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>receipt</v>
       </c>
       <c r="B33" t="str">
-        <v>slam</v>
+        <v>/rɪˈsiːt/</v>
       </c>
       <c r="C33" t="str">
-        <v>砰地关上</v>
+        <v>n./vt.</v>
       </c>
       <c r="D33" t="str">
-        <v>slam(砰地关上)📢</v>
+        <v>收据</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>sure</v>
       </c>
       <c r="B34" t="str">
-        <v>receipt</v>
+        <v>/ʃʊr/</v>
       </c>
       <c r="C34" t="str">
-        <v>收据</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D34" t="str">
-        <v>receipt(收据)📢</v>
+        <v>确信的</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>import</v>
       </c>
       <c r="B35" t="str">
-        <v>whatever</v>
+        <v>/ˈɪmpɔːrt/</v>
       </c>
       <c r="C35" t="str">
-        <v>无论什么</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D35" t="str">
-        <v>whatever(无论什么)📢</v>
+        <v>进口</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>echo</v>
       </c>
       <c r="B36" t="str">
-        <v>sure</v>
+        <v>/ˈekoʊ/</v>
       </c>
       <c r="C36" t="str">
-        <v>确信的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>sure(确信的)📢</v>
+        <v>回音</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>nearby</v>
       </c>
       <c r="B37" t="str">
-        <v>yellow</v>
+        <v>/ˌnɪrˈbaɪ/</v>
       </c>
       <c r="C37" t="str">
-        <v>黄色的</v>
+        <v>v./adj./adv./prep.</v>
       </c>
       <c r="D37" t="str">
-        <v>yellow(黄色的)📢</v>
+        <v>附近的</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>aunt</v>
       </c>
       <c r="B38" t="str">
-        <v>import</v>
+        <v>/ænt/</v>
       </c>
       <c r="C38" t="str">
-        <v>进口</v>
+        <v>n.</v>
       </c>
       <c r="D38" t="str">
-        <v>import(进口)📢</v>
+        <v>阿姨</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>education</v>
       </c>
       <c r="B39" t="str">
-        <v>echo</v>
+        <v>/ˌedʒuˈkeɪʃn/</v>
       </c>
       <c r="C39" t="str">
-        <v>回音</v>
+        <v>n.</v>
       </c>
       <c r="D39" t="str">
-        <v>echo(回音)📢</v>
+        <v>教育</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>contact</v>
       </c>
       <c r="B40" t="str">
-        <v>nearby</v>
+        <v>/ˈkɑːntækt/</v>
       </c>
       <c r="C40" t="str">
-        <v>附近的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D40" t="str">
-        <v>nearby(附近的)📢</v>
+        <v>联系</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>tomb</v>
       </c>
       <c r="B41" t="str">
-        <v>aunt</v>
+        <v>/tuːm/</v>
       </c>
       <c r="C41" t="str">
-        <v>阿姨</v>
+        <v>n./vt.</v>
       </c>
       <c r="D41" t="str">
-        <v>aunt(阿姨)📢</v>
+        <v>坟墓</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>nail</v>
       </c>
       <c r="B42" t="str">
-        <v>aunt</v>
+        <v>/neɪl/</v>
       </c>
       <c r="C42" t="str">
-        <v>阿姨</v>
+        <v>n./vt.</v>
       </c>
       <c r="D42" t="str">
-        <v>aunt(阿姨)📢</v>
+        <v>钉子</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>remedy</v>
       </c>
       <c r="B43" t="str">
-        <v>education</v>
+        <v>/ˈremədi/</v>
       </c>
       <c r="C43" t="str">
-        <v>教育</v>
+        <v>n./v.</v>
       </c>
       <c r="D43" t="str">
-        <v>education(教育)📢</v>
+        <v>补救</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>magazine</v>
       </c>
       <c r="B44" t="str">
-        <v>ornament</v>
+        <v>/ˈmæɡəziːn/</v>
       </c>
       <c r="C44" t="str">
-        <v>装饰物</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>ornament(装饰物)📢</v>
+        <v>杂志</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>lime</v>
       </c>
       <c r="B45" t="str">
-        <v>nearby</v>
+        <v>/laɪm/</v>
       </c>
       <c r="C45" t="str">
-        <v>附近的</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D45" t="str">
-        <v>nearby(附近的)📢</v>
+        <v>酸橙</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>orchestra</v>
       </c>
       <c r="B46" t="str">
-        <v>contact</v>
+        <v>/ˈɔːrkɪstrə/</v>
       </c>
       <c r="C46" t="str">
-        <v>联系</v>
+        <v>n.</v>
       </c>
       <c r="D46" t="str">
-        <v>contact(联系)📢</v>
+        <v>管弦乐队</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>further</v>
       </c>
       <c r="B47" t="str">
-        <v>tomb</v>
+        <v>/ˈfɜːrðər/</v>
       </c>
       <c r="C47" t="str">
-        <v>坟墓</v>
+        <v>v./adj./adv.</v>
       </c>
       <c r="D47" t="str">
-        <v>tomb(坟墓)📢</v>
+        <v>进一步</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>steam</v>
       </c>
       <c r="B48" t="str">
-        <v>education</v>
+        <v>/stiːm/</v>
       </c>
       <c r="C48" t="str">
-        <v>教育</v>
+        <v>n./vi./adj.</v>
       </c>
       <c r="D48" t="str">
-        <v>education(教育)📢</v>
+        <v>冒水汽</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>postage</v>
       </c>
       <c r="B49" t="str">
-        <v>nail</v>
+        <v>/ˈpoʊstɪdʒ/</v>
       </c>
       <c r="C49" t="str">
-        <v>钉子</v>
+        <v>n.</v>
       </c>
       <c r="D49" t="str">
-        <v>nail(钉子)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>remedy</v>
-      </c>
-      <c r="C50" t="str">
-        <v>补救</v>
-      </c>
-      <c r="D50" t="str">
-        <v>remedy(补救)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>magazine</v>
-      </c>
-      <c r="C51" t="str">
-        <v>杂志</v>
-      </c>
-      <c r="D51" t="str">
-        <v>magazine(杂志)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>cloud</v>
-      </c>
-      <c r="C52" t="str">
-        <v>云</v>
-      </c>
-      <c r="D52" t="str">
-        <v>cloud(云)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>lime</v>
-      </c>
-      <c r="C53" t="str">
-        <v>酸橙</v>
-      </c>
-      <c r="D53" t="str">
-        <v>lime(酸橙)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>orchestra</v>
-      </c>
-      <c r="C54" t="str">
-        <v>管弦乐队</v>
-      </c>
-      <c r="D54" t="str">
-        <v>orchestra(管弦乐队)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>further</v>
-      </c>
-      <c r="C55" t="str">
-        <v>进一步</v>
-      </c>
-      <c r="D55" t="str">
-        <v>further(进一步)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>steam</v>
-      </c>
-      <c r="C56" t="str">
-        <v>冒水汽</v>
-      </c>
-      <c r="D56" t="str">
-        <v>steam(冒水汽)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>postage</v>
-      </c>
-      <c r="C57" t="str">
         <v>邮费</v>
-      </c>
-      <c r="D57" t="str">
-        <v>postage(邮费)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D57"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D49"/>
   </ignoredErrors>
 </worksheet>
 </file>